--- a/ArchivosExcel/Lugares.xlsx
+++ b/ArchivosExcel/Lugares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joser\UPIngenieria\ProyectosVarios\WebScrappingExcel\ArchivosExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11EF6D7B-C472-4DBD-8161-E4DCDDB2727E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87CC175-2EF2-4E30-8EAB-05F51114CE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E9C5FDF-4083-4484-B12B-E256F5F8866C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Nombre</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Ciudad</t>
   </si>
   <si>
-    <t>Estado</t>
-  </si>
-  <si>
     <t>IMSS Hospital Centro Medico Siglo XXI</t>
   </si>
   <si>
@@ -63,6 +60,33 @@
   </si>
   <si>
     <t>Guanajuato</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
+    <t>Estado / Provincia / Departamento</t>
+  </si>
+  <si>
+    <t>País LATAM</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>Hospital General de Agudos José María Ramos Mejía</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>Hosítal Universitario San Antonio</t>
+  </si>
+  <si>
+    <t>Bogotá</t>
+  </si>
+  <si>
+    <t>Buenos Aires</t>
   </si>
 </sst>
 </file>
@@ -98,8 +122,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,42 +461,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F39B1D-CE7C-4053-929B-CFB28567C68C}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" customWidth="1"/>
+    <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/ArchivosExcel/Lugares.xlsx
+++ b/ArchivosExcel/Lugares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joser\UPIngenieria\ProyectosVarios\WebScrappingExcel\ArchivosExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87CC175-2EF2-4E30-8EAB-05F51114CE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73F2E40-ED0C-47D8-93A9-61323FFDD075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E9C5FDF-4083-4484-B12B-E256F5F8866C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Nombre</t>
   </si>
@@ -69,24 +69,6 @@
   </si>
   <si>
     <t>País LATAM</t>
-  </si>
-  <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>Hospital General de Agudos José María Ramos Mejía</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>Hosítal Universitario San Antonio</t>
-  </si>
-  <si>
-    <t>Bogotá</t>
-  </si>
-  <si>
-    <t>Buenos Aires</t>
   </si>
 </sst>
 </file>
@@ -461,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F39B1D-CE7C-4053-929B-CFB28567C68C}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" customWidth="1"/>
@@ -513,28 +495,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ArchivosExcel/Lugares.xlsx
+++ b/ArchivosExcel/Lugares.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joser\UPIngenieria\ProyectosVarios\WebScrappingExcel\ArchivosExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73F2E40-ED0C-47D8-93A9-61323FFDD075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0661D9F4-2F33-4C14-919E-34FF912F190E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E9C5FDF-4083-4484-B12B-E256F5F8866C}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{9E9C5FDF-4083-4484-B12B-E256F5F8866C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>Nombre</t>
   </si>
@@ -62,26 +62,70 @@
     <t>Guanajuato</t>
   </si>
   <si>
-    <t>MX</t>
-  </si>
-  <si>
     <t>Estado / Provincia / Departamento</t>
   </si>
   <si>
     <t>País LATAM</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Hospital Italiano de Buenos Aires</t>
+  </si>
+  <si>
+    <t>Buenos Aires</t>
+  </si>
+  <si>
+    <t>Ciudad Autónoma de Buenos Aires</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Fundación Santa Fe de Bogotá</t>
+  </si>
+  <si>
+    <t>Bogotá</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Edgardo Rebagliati Martins National Hospital</t>
+  </si>
+  <si>
+    <t>Peru</t>
+  </si>
+  <si>
+    <t>Lima</t>
+  </si>
+  <si>
+    <t>Hospital Clínico Universidad de Chile</t>
+  </si>
+  <si>
+    <t>Chile</t>
+  </si>
+  <si>
+    <t>Santiago</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,10 +148,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,17 +493,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F39B1D-CE7C-4053-929B-CFB28567C68C}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="28.8">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -462,20 +512,20 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -484,15 +534,63 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
